--- a/slide_classification/TCGA_Results/PRISM/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/PRISM/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -758,13 +758,13 @@
         <v>0.865979381443299</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8811881188118812</v>
+        <v>0.8712871287128713</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8529239832468741</v>
+        <v>0.8549130214364073</v>
       </c>
     </row>
     <row r="15">
@@ -780,13 +780,13 @@
         <v>0.565018315018315</v>
       </c>
       <c r="D15" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6081460674157304</v>
+        <v>0.5664794007490637</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5653554895479054</v>
+        <v>0.5674388228812386</v>
       </c>
     </row>
     <row r="16">
@@ -802,13 +802,13 @@
         <v>0.5809238949817215</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5463546354635463</v>
+        <v>0.6266666666666667</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6340579710144928</v>
+        <v>0.5825119236883943</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5758331372226476</v>
+        <v>0.5830246331919031</v>
       </c>
     </row>
     <row r="17">
@@ -824,13 +824,13 @@
         <v>0.8339106392163717</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7806994985212807</v>
+        <v>0.8152380952380953</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8633232888506243</v>
+        <v>0.8472225282941649</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8188002912953672</v>
+        <v>0.823409750335456</v>
       </c>
     </row>
     <row r="18">
@@ -846,13 +846,13 @@
         <v>0.7687728937728937</v>
       </c>
       <c r="D18" t="n">
-        <v>0.725</v>
+        <v>0.6510869565217392</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6839887640449439</v>
+        <v>0.6779026217228464</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7044782932423382</v>
+        <v>0.6844784967922487</v>
       </c>
     </row>
     <row r="19">
@@ -873,17 +873,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[92, 0], [18, 2]]</t>
+          <t>[[92, 0], [16, 4]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[86, 3], [9, 3]]</t>
+          <t>[[86, 3], [10, 2]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[86, 2], [13, 2]]</t>
+          <t>[[86, 2], [12, 2]]</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1406,38 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8529239832468741</v>
+        <v>0.8549130214364073</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02191779860355526</v>
+        <v>0.01785969456407287</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5653554895479054</v>
+        <v>0.5674388228812386</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0264633483896585</v>
+        <v>0.02190065517395432</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5758331372226476</v>
+        <v>0.5830246331919031</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0368441915238699</v>
+        <v>0.02996935062454981</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8188002912953672</v>
+        <v>0.823409750335456</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03211674470383417</v>
+        <v>0.01889112083998046</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7044782932423382</v>
+        <v>0.6844784967922487</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04773020870451971</v>
+        <v>0.05056842828849328</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[[86, 2], [13, 2]]</t>
+          <t>[[86, 2], [12, 2]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/PRISM/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/PRISM/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -610,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8446601941747572</v>
+        <v>0.8349514563106796</v>
       </c>
       <c r="C8" t="n">
-        <v>0.865979381443299</v>
+        <v>0.845360824742268</v>
       </c>
       <c r="D8" t="n">
         <v>0.8303571428571429</v>
       </c>
       <c r="E8" t="n">
-        <v>0.801980198019802</v>
+        <v>0.8514851485148515</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8357442291237502</v>
+        <v>0.8405386431062355</v>
       </c>
     </row>
     <row r="9">
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8261363636363637</v>
+        <v>0.8481060606060606</v>
       </c>
       <c r="C9" t="n">
-        <v>0.76007326007326</v>
+        <v>0.7156593406593407</v>
       </c>
       <c r="D9" t="n">
         <v>0.8380434782608696</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7794943820224719</v>
+        <v>0.7715355805243446</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8009368709982413</v>
+        <v>0.7933361150126539</v>
       </c>
     </row>
     <row r="10">
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7518072289156627</v>
+        <v>0.7501783421315451</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7364681295715778</v>
+        <v>0.6959247648902821</v>
       </c>
       <c r="D10" t="n">
         <v>0.7651991614255764</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6758664955070603</v>
+        <v>0.7142048670062252</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7323352538549693</v>
+        <v>0.7313767838634072</v>
       </c>
     </row>
     <row r="11">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8593987600888994</v>
+        <v>0.8533189643828255</v>
       </c>
       <c r="C11" t="n">
-        <v>0.871693113143522</v>
+        <v>0.8519535920886792</v>
       </c>
       <c r="D11" t="n">
         <v>0.8447139862234201</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8300054652448556</v>
+        <v>0.865213176665714</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8514528311751743</v>
+        <v>0.8537999298401597</v>
       </c>
     </row>
     <row r="12">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8901515151515151</v>
+        <v>0.9181818181818182</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7948717948717949</v>
+        <v>0.8040293040293041</v>
       </c>
       <c r="D12" t="n">
         <v>0.9222826086956523</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8380149812734081</v>
+        <v>0.8295880149812733</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8613302249980926</v>
+        <v>0.8685204364720119</v>
       </c>
     </row>
     <row r="13">
@@ -721,12 +721,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[75, 13], [3, 12]]</t>
+          <t>[[73, 15], [2, 13]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[76, 8], [5, 8]]</t>
+          <t>[[75, 9], [6, 7]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[72, 17], [3, 9]]</t>
+          <t>[[78, 11], [4, 8]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[75, 14], [4, 12]]</t>
+          <t>[[76, 13], [4, 11]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8357442291237502</v>
+        <v>0.8405386431062355</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02325236204888304</v>
+        <v>0.008336051523390061</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8009368709982413</v>
+        <v>0.7933361150126539</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0321773591328824</v>
+        <v>0.05363636790188198</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7323352538549693</v>
+        <v>0.7313767838634072</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03415038639831598</v>
+        <v>0.02760965499190866</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8514528311751743</v>
+        <v>0.8537999298401597</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01563816115383273</v>
+        <v>0.007356236561097096</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8613302249980926</v>
+        <v>0.8685204364720119</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04874982915179225</v>
+        <v>0.05251538727460471</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[75, 14], [4, 12]]</t>
+          <t>[[76, 13], [4, 11]]</t>
         </is>
       </c>
     </row>
